--- a/output/graficos_dimensiones/comunal_d_env_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:18</t>
+    <t xml:space="preserve">2026-09-10 01:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:32</t>
+    <t xml:space="preserve">2026-09-12 22:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_metropolitana.xlsx
@@ -75,12 +75,12 @@
     <t xml:space="preserve">La Granja</t>
   </si>
   <si>
+    <t xml:space="preserve">Calera de Tango</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Ramón</t>
   </si>
   <si>
-    <t xml:space="preserve">Calera de Tango</t>
-  </si>
-  <si>
     <t xml:space="preserve">San José de Maipo</t>
   </si>
   <si>
@@ -99,48 +99,48 @@
     <t xml:space="preserve">El Bosque</t>
   </si>
   <si>
+    <t xml:space="preserve">Pirque</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Pedro</t>
   </si>
   <si>
-    <t xml:space="preserve">Pirque</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Miguel</t>
   </si>
   <si>
     <t xml:space="preserve">Cerro Navia</t>
   </si>
   <si>
+    <t xml:space="preserve">Cerrillos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Santiago</t>
   </si>
   <si>
-    <t xml:space="preserve">Cerrillos</t>
+    <t xml:space="preserve">Peñalolén</t>
   </si>
   <si>
     <t xml:space="preserve">María Pinto</t>
   </si>
   <si>
-    <t xml:space="preserve">Peñalolén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Curacaví</t>
   </si>
   <si>
+    <t xml:space="preserve">Melipilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">Estación Central</t>
   </si>
   <si>
-    <t xml:space="preserve">Melipilla</t>
-  </si>
-  <si>
     <t xml:space="preserve">Talagante</t>
   </si>
   <si>
+    <t xml:space="preserve">Isla de Maipo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Independencia</t>
   </si>
   <si>
-    <t xml:space="preserve">Isla de Maipo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Puente Alto</t>
   </si>
   <si>
@@ -174,12 +174,12 @@
     <t xml:space="preserve">Huechuraba</t>
   </si>
   <si>
+    <t xml:space="preserve">Buin</t>
+  </si>
+  <si>
     <t xml:space="preserve">Padre Hurtado</t>
   </si>
   <si>
-    <t xml:space="preserve">Buin</t>
-  </si>
-  <si>
     <t xml:space="preserve">Quilicura</t>
   </si>
   <si>
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:44</t>
+    <t xml:space="preserve">2026-09-24 00:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -634,7 +634,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>200.09</v>
+        <v>213.08</v>
       </c>
     </row>
     <row r="3">
@@ -651,7 +651,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>174.33</v>
+        <v>188.35</v>
       </c>
     </row>
     <row r="4">
@@ -668,7 +668,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>158.48</v>
+        <v>171.81</v>
       </c>
     </row>
     <row r="5">
@@ -685,7 +685,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>155.45</v>
+        <v>165.58</v>
       </c>
     </row>
     <row r="6">
@@ -702,7 +702,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>147.35</v>
+        <v>158.37</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>142.06</v>
+        <v>152.44</v>
       </c>
     </row>
     <row r="8">
@@ -736,7 +736,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>142.02</v>
+        <v>151.42</v>
       </c>
     </row>
     <row r="9">
@@ -753,7 +753,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>134.26</v>
+        <v>143.03</v>
       </c>
     </row>
     <row r="10">
@@ -770,7 +770,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>129.6</v>
+        <v>139.3</v>
       </c>
     </row>
     <row r="11">
@@ -787,7 +787,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>123.07</v>
+        <v>131.8</v>
       </c>
     </row>
     <row r="12">
@@ -804,7 +804,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>122.24</v>
+        <v>131.05</v>
       </c>
     </row>
     <row r="13">
@@ -821,7 +821,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>122.22</v>
+        <v>130.99</v>
       </c>
     </row>
     <row r="14">
@@ -838,7 +838,7 @@
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>121.97</v>
+        <v>130.62</v>
       </c>
     </row>
     <row r="15">
@@ -849,13 +849,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>13131</v>
+        <v>13403</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>119.58</v>
+        <v>128.13</v>
       </c>
     </row>
     <row r="16">
@@ -866,13 +866,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>13403</v>
+        <v>13131</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>118.7</v>
+        <v>127.75</v>
       </c>
     </row>
     <row r="17">
@@ -889,7 +889,7 @@
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>116.12</v>
+        <v>125.26</v>
       </c>
     </row>
     <row r="18">
@@ -906,7 +906,7 @@
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>113.93</v>
+        <v>122.75</v>
       </c>
     </row>
     <row r="19">
@@ -923,7 +923,7 @@
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>112.84</v>
+        <v>120.29</v>
       </c>
     </row>
     <row r="20">
@@ -940,7 +940,7 @@
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>111.89</v>
+        <v>119.11</v>
       </c>
     </row>
     <row r="21">
@@ -957,7 +957,7 @@
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>109.84</v>
+        <v>117.27</v>
       </c>
     </row>
     <row r="22">
@@ -974,7 +974,7 @@
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>109.04</v>
+        <v>117.13</v>
       </c>
     </row>
     <row r="23">
@@ -985,13 +985,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>13505</v>
+        <v>13202</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>106.66</v>
+        <v>114.48</v>
       </c>
     </row>
     <row r="24">
@@ -1002,13 +1002,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>13202</v>
+        <v>13505</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>106.56</v>
+        <v>113.84</v>
       </c>
     </row>
     <row r="25">
@@ -1025,7 +1025,7 @@
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>105.27</v>
+        <v>111.59</v>
       </c>
     </row>
     <row r="26">
@@ -1042,7 +1042,7 @@
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>103.77</v>
+        <v>110.91</v>
       </c>
     </row>
     <row r="27">
@@ -1053,13 +1053,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>13101</v>
+        <v>13102</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>103.17</v>
+        <v>109.77</v>
       </c>
     </row>
     <row r="28">
@@ -1070,13 +1070,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>13102</v>
+        <v>13101</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>102.43</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="29">
@@ -1087,13 +1087,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>13504</v>
+        <v>13122</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>100.99</v>
+        <v>108.41</v>
       </c>
     </row>
     <row r="30">
@@ -1104,13 +1104,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>13122</v>
+        <v>13504</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>100.63</v>
+        <v>108.04</v>
       </c>
     </row>
     <row r="31">
@@ -1127,7 +1127,7 @@
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>100.13</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="32">
@@ -1138,13 +1138,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>13106</v>
+        <v>13501</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>96.02</v>
+        <v>102.06</v>
       </c>
     </row>
     <row r="33">
@@ -1155,13 +1155,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>13501</v>
+        <v>13106</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>95.68</v>
+        <v>101.45</v>
       </c>
     </row>
     <row r="34">
@@ -1178,7 +1178,7 @@
         <v>2022</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>92.31</v>
+        <v>98.89</v>
       </c>
     </row>
     <row r="35">
@@ -1189,13 +1189,13 @@
         <v>39</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>13108</v>
+        <v>13603</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>91.09</v>
+        <v>97.97</v>
       </c>
     </row>
     <row r="36">
@@ -1206,13 +1206,13 @@
         <v>40</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>13603</v>
+        <v>13108</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>90.84</v>
+        <v>96.31</v>
       </c>
     </row>
     <row r="37">
@@ -1229,7 +1229,7 @@
         <v>2022</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>89.04</v>
+        <v>95.85</v>
       </c>
     </row>
     <row r="38">
@@ -1246,7 +1246,7 @@
         <v>2022</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>88.78</v>
+        <v>95.34</v>
       </c>
     </row>
     <row r="39">
@@ -1263,7 +1263,7 @@
         <v>2022</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>88.67</v>
+        <v>95.13</v>
       </c>
     </row>
     <row r="40">
@@ -1280,7 +1280,7 @@
         <v>2022</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>86.01</v>
+        <v>92.02</v>
       </c>
     </row>
     <row r="41">
@@ -1297,7 +1297,7 @@
         <v>2022</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>85.44</v>
+        <v>91.35</v>
       </c>
     </row>
     <row r="42">
@@ -1314,7 +1314,7 @@
         <v>2022</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>84.35</v>
+        <v>90.41</v>
       </c>
     </row>
     <row r="43">
@@ -1331,7 +1331,7 @@
         <v>2022</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>82.93</v>
+        <v>88.34</v>
       </c>
     </row>
     <row r="44">
@@ -1348,7 +1348,7 @@
         <v>2022</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>80.56</v>
+        <v>87.52</v>
       </c>
     </row>
     <row r="45">
@@ -1365,7 +1365,7 @@
         <v>2022</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>79.81</v>
+        <v>85.51</v>
       </c>
     </row>
     <row r="46">
@@ -1382,7 +1382,7 @@
         <v>2022</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>77.76</v>
+        <v>83.41</v>
       </c>
     </row>
     <row r="47">
@@ -1399,7 +1399,7 @@
         <v>2022</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>75.61</v>
+        <v>81.58</v>
       </c>
     </row>
     <row r="48">
@@ -1410,13 +1410,13 @@
         <v>52</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>13604</v>
+        <v>13402</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>67.77</v>
+        <v>72.21</v>
       </c>
     </row>
     <row r="49">
@@ -1427,13 +1427,13 @@
         <v>53</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>13402</v>
+        <v>13604</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>67.51</v>
+        <v>72.15</v>
       </c>
     </row>
     <row r="50">
@@ -1450,7 +1450,7 @@
         <v>2022</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>62.04</v>
+        <v>66.6</v>
       </c>
     </row>
     <row r="51">
@@ -1467,7 +1467,7 @@
         <v>2022</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>50.04</v>
+        <v>52.19</v>
       </c>
     </row>
     <row r="52">
@@ -1484,7 +1484,7 @@
         <v>2022</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>47.32</v>
+        <v>50.63</v>
       </c>
     </row>
     <row r="53">
@@ -1501,7 +1501,7 @@
         <v>2022</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>42.78</v>
+        <v>45.6</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:12</t>
+    <t xml:space="preserve">2026-10-02 16:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:09</t>
+    <t xml:space="preserve">2026-10-05 16:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
